--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 18/06/2026, 11:48</x:t>
+    <x:t>Conta: 11370136 | 23/06/2026, 14:05</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 23/06/2026, 14:05</x:t>
+    <x:t>Conta: 11370136 | 24/06/2026, 16:30</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 24/06/2026, 16:30</x:t>
+    <x:t>Conta: 11370136 | 26/06/2026, 17:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 26/06/2026, 17:04</x:t>
+    <x:t>Conta: 11370136 | 29/06/2026, 11:44</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 29/06/2026, 11:44</x:t>
+    <x:t>Conta: 11370136 | 30/06/2026, 20:08</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 30/06/2026, 20:08</x:t>
+    <x:t>Conta: 11370136 | 01/07/2026, 18:18</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 01/07/2026, 18:18</x:t>
+    <x:t>Conta: 11370136 | 03/07/2026, 15:19</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 03/07/2026, 15:19</x:t>
+    <x:t>Conta: 11370136 | 06/07/2026, 17:14</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 06/07/2026, 17:14</x:t>
+    <x:t>Conta: 11370136 | 07/07/2026, 15:55</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 07/07/2026, 15:55</x:t>
+    <x:t>Conta: 11370136 | 09/07/2026, 18:04</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 09/07/2026, 18:04</x:t>
+    <x:t>Conta: 11370136 | 14/07/2026, 09:58</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 14/07/2026, 09:58</x:t>
+    <x:t>Conta: 11370136 | 15/07/2026, 19:02</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 15/07/2026, 19:02</x:t>
+    <x:t>Conta: 11370136 | 21/07/2026, 09:18</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,69 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 369,86</x:t>
+    <x:t>100,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.501.562,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,90%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.258.064,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.499.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.501.211,17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 369,87</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -70,7 +124,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>369,86</x:t>
+    <x:t>369,87</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -614,7 +668,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -674,13 +728,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>369.86</x:v>
+        <x:v>3501932.6664168</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>0</x:v>
+        <x:v>3501562.7964168</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>369.86</x:v>
+        <x:v>369.87</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +782,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,86 +798,192 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="s">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="C10" s="12"/>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 21/07/2026, 09:18</x:t>
+    <x:t>Conta: 11370136 | 27/07/2026, 15:24</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.501.562,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Pós-Fixada</x:t>
+    <x:t>99,9%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.008.670,61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,90%|Prefixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,31 +70,31 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>20/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20/08/2026</x:t>
+    <x:t>22/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>2.258.064,00</x:t>
+    <x:t>871,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 3.499.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.501.211,17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 369,87</x:t>
+    <x:t>R$ 1.007.320,66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.008.366,87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,10%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.006,87</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -124,7 +124,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>369,87</x:t>
+    <x:t>1006,87</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -728,13 +728,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>3501932.6664168</x:v>
+        <x:v>1009677.477529</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3501562.7964168</x:v>
+        <x:v>1008670.607529</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>369.87</x:v>
+        <x:v>1006.87</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 27/07/2026, 15:24</x:t>
+    <x:t>Conta: 11370136 | 29/07/2026, 18:28</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>99,9%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.008.670,61</x:t>
+    <x:t>R$ 1.009.571,58</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Prefixada</x:t>
@@ -88,7 +88,7 @@
     <x:t>R$ 1.007.320,66</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.008.366,87</x:t>
+    <x:t>R$ 1.009.065,12</x:t>
   </x:si>
   <x:si>
     <x:t>0,10%|Saldo projetado</x:t>
@@ -728,10 +728,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1009677.477529</x:v>
+        <x:v>1010578.448639</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1008670.607529</x:v>
+        <x:v>1009571.578639</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>1006.87</x:v>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 29/07/2026, 18:28</x:t>
+    <x:t>Conta: 11370136 | 30/07/2026, 16:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,69 +34,15 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>99,9%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.009.571,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Prefixada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aplicação</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vencimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taxa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disponível</x:t>
+    <x:t>100%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 921,35</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
-    <x:t>Valor aplicado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Posição</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Valor líquido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85,00% CDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>871,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.007.320,66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.009.065,12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,10%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.006,87</x:t>
-  </x:si>
-  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -124,7 +70,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>1006,87</x:t>
+    <x:t>921,35</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -668,7 +614,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -728,13 +674,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>1010578.448639</x:v>
+        <x:v>921.35</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>1009571.578639</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>1006.87</x:v>
+        <x:v>921.35</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -782,13 +728,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="9"/>
+      <x:c r="H7" s="9"/>
+      <x:c r="I7" s="9"/>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -798,192 +744,86 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="s">
+      <x:c r="C9" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="D9" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="E9" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="F9" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="G9" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="H9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="s">
+      <x:c r="I9" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="s">
+      <x:c r="J9" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="9"/>
-      <x:c r="J12" s="9"/>
-      <x:c r="K12" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="3">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:J12"/>
+    <x:mergeCell ref="A7:J7"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 30/07/2026, 16:37</x:t>
+    <x:t>Conta: 11370136 | 04/08/2026, 17:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 04/08/2026, 17:40</x:t>
+    <x:t>Conta: 11370136 | 11/08/2026, 16:37</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,15 +34,69 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 921,35</x:t>
+    <x:t>100,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.501.975,98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99,90%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aplicação</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carência</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vencimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taxa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disponível</x:t>
   </x:si>
   <x:si>
     <x:t>Garantia</x:t>
   </x:si>
   <x:si>
+    <x:t>Valor aplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Posição</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor líquido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.631.578,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.499.999,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 4.501.531,38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 515,25</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resgate de fundo pendente</x:t>
   </x:si>
   <x:si>
@@ -70,7 +124,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>921,35</x:t>
+    <x:t>515,25</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -614,7 +668,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -674,13 +728,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>921.35</x:v>
+        <x:v>4502491.23455122</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>0</x:v>
+        <x:v>4501975.98455122</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>921.35</x:v>
+        <x:v>515.25</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -728,13 +782,13 @@
       <x:c r="D7" s="9"/>
       <x:c r="E7" s="9"/>
       <x:c r="F7" s="9"/>
-      <x:c r="G7" s="9"/>
-      <x:c r="H7" s="9"/>
-      <x:c r="I7" s="9"/>
-      <x:c r="J7" s="9"/>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="G7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="4"/>
@@ -744,86 +798,192 @@
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A9" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="11" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
+      <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12" t="s">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="C10" s="12"/>
       <x:c r="D10" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A12" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B12" s="9"/>
+      <x:c r="C12" s="9"/>
+      <x:c r="D12" s="9"/>
+      <x:c r="E12" s="9"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="9"/>
+      <x:c r="H12" s="9"/>
+      <x:c r="I12" s="9"/>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:11">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A14" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A15" s="12" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="3">
+  <x:mergeCells count="4">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
-    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A7:F7"/>
+    <x:mergeCell ref="A12:J12"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 11/08/2026, 16:37</x:t>
+    <x:t>Conta: 11370136 | 17/08/2026, 14:25</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.501.975,98</x:t>
+    <x:t>R$ 4.207.681,95</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -79,22 +79,34 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>2.631.578,00</x:t>
+    <x:t>412.358,00</x:t>
   </x:si>
   <x:si>
     <x:t>0,00</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.499.999,99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.501.531,38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,01%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 515,25</x:t>
+    <x:t>R$ 705.132,43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 706.681,95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 706.333,31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.423,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.501.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 14,29</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -124,7 +136,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>515,25</x:t>
+    <x:t>14,29</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -320,7 +332,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -366,6 +378,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -668,7 +684,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -728,13 +744,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4502491.23455122</x:v>
+        <x:v>4207696.23918515</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4501975.98455122</x:v>
+        <x:v>4207681.94918515</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>515.25</x:v>
+        <x:v>14.29</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -858,124 +874,153 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="4"/>
-      <x:c r="B11" s="4"/>
-      <x:c r="C11" s="4"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A12" s="8" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9"/>
-      <x:c r="I12" s="9"/>
-      <x:c r="J12" s="9"/>
-      <x:c r="K12" s="10" t="s">
+    <x:row r="11" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A11" s="13"/>
+      <x:c r="B11" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A14" s="11" t="s">
+      <x:c r="C11" s="13"/>
+      <x:c r="D11" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K11" s="3"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A13" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="9"/>
+      <x:c r="E13" s="9"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="G13" s="9"/>
+      <x:c r="H13" s="9"/>
+      <x:c r="I13" s="9"/>
+      <x:c r="J13" s="9"/>
+      <x:c r="K13" s="10" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:11">
+      <x:c r="A14" s="4"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A15" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B14" s="11" t="s">
+      <x:c r="B15" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="C15" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="s">
+      <x:c r="D15" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="s">
+      <x:c r="E15" s="11" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="J14" s="11" t="s">
+      <x:c r="F15" s="11" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K14" s="11" t="s">
+      <x:c r="G15" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A15" s="12" t="s">
+      <x:c r="H15" s="11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B15" s="12" t="s">
+      <x:c r="I15" s="11" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="K15" s="12" t="s">
-        <x:v>37</x:v>
+      <x:c r="J15" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -983,7 +1028,7 @@
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A12:J12"/>
+    <x:mergeCell ref="A13:J13"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 17/08/2026, 14:25</x:t>
+    <x:t>Conta: 11370136 | 18/08/2026, 09:40</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>100,0%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 4.207.681,95</x:t>
+    <x:t>R$ 4.209.529,58</x:t>
   </x:si>
   <x:si>
     <x:t>99,90%|Pós-Fixada</x:t>
@@ -88,10 +88,10 @@
     <x:t>R$ 705.132,43</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 706.681,95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 706.333,31</x:t>
+    <x:t>R$ 706.992,26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 706.573,80</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -104,6 +104,12 @@
   </x:si>
   <x:si>
     <x:t>R$ 3.501.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.502.537,32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 3.502.191,42</x:t>
   </x:si>
   <x:si>
     <x:t>R$ 14,29</x:t>
@@ -744,10 +750,10 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4207696.23918515</x:v>
+        <x:v>4209543.87469272</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4207681.94918515</x:v>
+        <x:v>4209529.58469272</x:v>
       </x:c>
       <x:c r="C4" s="7">
         <x:v>14.29</x:v>
@@ -903,10 +909,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="I11" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
@@ -937,7 +943,7 @@
       <x:c r="I13" s="9"/>
       <x:c r="J13" s="9"/>
       <x:c r="K13" s="10" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -961,66 +967,66 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="11" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D15" s="11" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E15" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F15" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G15" s="11" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H15" s="11" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I15" s="11" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J15" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K15" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
       <x:c r="A16" s="13" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K16" s="13" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 18/08/2026, 09:40</x:t>
+    <x:t>Conta: 11370136 | 18/08/2026, 18:42</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>100,0%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 4.209.529,58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99,90%|Pós-Fixada</x:t>
+    <x:t>36,4%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.532.969,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,40%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -70,49 +70,76 @@
     <x:t>Valor líquido</x:t>
   </x:si>
   <x:si>
-    <x:t>10/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/09/2026</x:t>
+    <x:t>LCI CEF - FEV/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/02/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/02/2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85,50% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.222.011,09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LCI CEF - NOV/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/11/2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/11/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84,00% CDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 310.958,77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52,5%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.208.781,28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52,40%|Pós-Fixada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>412.358,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 705.132,43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 706.992,26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 706.573,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18/09/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.423,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.501.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.502.537,32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 3.502.191,42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 14,29</x:t>
+    <x:t>1.528,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.207.811,80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.208.563,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,1%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 467.246,52</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -142,7 +169,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>14,29</x:t>
+    <x:t>467246,52</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -690,7 +717,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K16"/>
+  <x:dimension ref="A1:K21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
@@ -750,13 +777,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4209543.87469272</x:v>
+        <x:v>4208997.655552</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4209529.58469272</x:v>
+        <x:v>3741751.135552</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>14.29</x:v>
+        <x:v>467246.52</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -859,28 +886,32 @@
       <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A10" s="12"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="B10" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="12"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E10" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G10" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H10" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
         <x:v>25</x:v>
@@ -888,31 +919,35 @@
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A11" s="13"/>
+      <x:c r="A11" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="B11" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="13"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G11" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H11" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I11" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
@@ -931,20 +966,20 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="45" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="9"/>
       <x:c r="C13" s="9"/>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9"/>
-      <x:c r="I13" s="9"/>
-      <x:c r="J13" s="9"/>
-      <x:c r="K13" s="10" t="s">
+      <x:c r="G13" s="10" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="H13" s="3"/>
+      <x:c r="I13" s="3"/>
+      <x:c r="J13" s="3"/>
+      <x:c r="K13" s="3"/>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="4"/>
@@ -954,87 +989,193 @@
       <x:c r="E14" s="4"/>
       <x:c r="F14" s="4"/>
       <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
+      <x:c r="H14" s="3"/>
+      <x:c r="I14" s="3"/>
+      <x:c r="J14" s="3"/>
+      <x:c r="K14" s="3"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A15" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A16" s="13"/>
+      <x:c r="B16" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
+      <x:c r="A17" s="4"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A18" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="9"/>
+      <x:c r="C18" s="9"/>
+      <x:c r="D18" s="9"/>
+      <x:c r="E18" s="9"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="G18" s="9"/>
+      <x:c r="H18" s="9"/>
+      <x:c r="I18" s="9"/>
+      <x:c r="J18" s="9"/>
+      <x:c r="K18" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
+      <x:c r="H19" s="4"/>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="4"/>
+      <x:c r="K19" s="4"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A20" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B20" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K15" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13" t="s">
+      <x:c r="C20" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="D20" s="11" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K16" s="13" t="s">
-        <x:v>43</x:v>
+      <x:c r="E20" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K20" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A21" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J21" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K21" s="13" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="4">
+  <x:mergeCells count="5">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
-    <x:mergeCell ref="A13:J13"/>
+    <x:mergeCell ref="A13:F13"/>
+    <x:mergeCell ref="A18:J18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 18/08/2026, 18:42</x:t>
+    <x:t>Conta: 11370136 | 20/08/2026, 09:49</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -37,7 +37,7 @@
     <x:t>36,4%|Renda Fixa</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.532.969,86</x:t>
+    <x:t>R$ 1.534.319,54</x:t>
   </x:si>
   <x:si>
     <x:t>36,40%|Pós-Fixada</x:t>
@@ -94,6 +94,12 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 1.223.090,84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.222.086,68</x:t>
+  </x:si>
+  <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
   </x:si>
   <x:si>
@@ -109,10 +115,16 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 311.228,71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 310.977,67</x:t>
+  </x:si>
+  <x:si>
     <x:t>52,5%|Operações Compromissadas</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.208.781,28</x:t>
+    <x:t>R$ 2.210.721,50</x:t>
   </x:si>
   <x:si>
     <x:t>52,40%|Pós-Fixada</x:t>
@@ -133,13 +145,49 @@
     <x:t>R$ 2.207.811,80</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 2.208.563,15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,1%|Saldo projetado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 467.246,52</x:t>
+    <x:t>R$ 2.210.066,82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,1%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 467.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valor cota</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qtd. cotas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Em cotização</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 271,75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.718,50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 0,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0,01%|Saldo projetado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 246,52</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -169,7 +217,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>467246,52</x:t>
+    <x:t>246,52</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -717,10 +765,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K21"/>
+  <x:dimension ref="A1:K26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -777,13 +825,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4208997.655552</x:v>
+        <x:v>4212287.55969902</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>3741751.135552</x:v>
+        <x:v>4212041.03969902</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>467246.52</x:v>
+        <x:v>246.52</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -911,28 +959,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J10" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11" ht="30" customHeight="1">
       <x:c r="A11" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F11" s="13" t="s">
         <x:v>23</x:v>
@@ -941,13 +989,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H11" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I11" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J11" s="13" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K11" s="3"/>
     </x:row>
@@ -966,7 +1014,7 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="45" customHeight="1">
       <x:c r="A13" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="9"/>
       <x:c r="C13" s="9"/>
@@ -974,7 +1022,7 @@
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H13" s="3"/>
       <x:c r="I13" s="3"/>
@@ -996,7 +1044,7 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A15" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="11" t="s">
         <x:v>9</x:v>
@@ -1030,29 +1078,29 @@
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
       <x:c r="A16" s="13"/>
       <x:c r="B16" s="13" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="13"/>
       <x:c r="D16" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E16" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G16" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H16" s="13" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I16" s="13" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J16" s="13" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
@@ -1071,20 +1119,20 @@
     </x:row>
     <x:row r="18" spans="1:11" ht="45" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
       <x:c r="D18" s="9"/>
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="9"/>
-      <x:c r="G18" s="9"/>
-      <x:c r="H18" s="9"/>
-      <x:c r="I18" s="9"/>
-      <x:c r="J18" s="9"/>
-      <x:c r="K18" s="10" t="s">
-        <x:v>41</x:v>
-      </x:c>
+      <x:c r="G18" s="10" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="3"/>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="4"/>
@@ -1094,45 +1142,37 @@
       <x:c r="E19" s="4"/>
       <x:c r="F19" s="4"/>
       <x:c r="G19" s="4"/>
-      <x:c r="H19" s="4"/>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="3"/>
+      <x:c r="J19" s="3"/>
+      <x:c r="K19" s="3"/>
     </x:row>
     <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
       <x:c r="A20" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D20" s="11" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E20" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F20" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G20" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I20" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K20" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="3"/>
+      <x:c r="J20" s="3"/>
+      <x:c r="K20" s="3"/>
     </x:row>
     <x:row r="21" spans="1:11" ht="30" customHeight="1">
       <x:c r="A21" s="13" t="s">
@@ -1142,40 +1182,146 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G21" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H21" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I21" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J21" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K21" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H21" s="3"/>
+      <x:c r="I21" s="3"/>
+      <x:c r="J21" s="3"/>
+      <x:c r="K21" s="3"/>
+    </x:row>
+    <x:row r="22" spans="1:11">
+      <x:c r="A22" s="4"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A23" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B23" s="9"/>
+      <x:c r="C23" s="9"/>
+      <x:c r="D23" s="9"/>
+      <x:c r="E23" s="9"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="G23" s="9"/>
+      <x:c r="H23" s="9"/>
+      <x:c r="I23" s="9"/>
+      <x:c r="J23" s="9"/>
+      <x:c r="K23" s="10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:11">
+      <x:c r="A24" s="4"/>
+      <x:c r="B24" s="4"/>
+      <x:c r="C24" s="4"/>
+      <x:c r="D24" s="4"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A25" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J25" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K25" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A26" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J26" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K26" s="13" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="5">
+  <x:mergeCells count="6">
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A18:J18"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A23:J23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/data/positions/Posição Consolidada - 11370136.xlsx
+++ b/data/positions/Posição Consolidada - 11370136.xlsx
@@ -19,7 +19,7 @@
     <x:t>XP</x:t>
   </x:si>
   <x:si>
-    <x:t>Conta: 11370136 | 20/08/2026, 09:49</x:t>
+    <x:t>Conta: 11370136 | 21/08/2026, 14:50</x:t>
   </x:si>
   <x:si>
     <x:t>Este é o seu patrimônio</x:t>
@@ -34,13 +34,13 @@
     <x:t>Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>36,4%|Renda Fixa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.534.319,54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,40%|Pós-Fixada</x:t>
+    <x:t>32,2%|Renda Fixa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.534.994,83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,20%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>Aplicação</x:t>
@@ -94,10 +94,10 @@
     <x:t>R$ 1.222.011,09</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 1.223.090,84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 1.222.086,68</x:t>
+    <x:t>R$ 1.223.631,07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.222.173,09</x:t>
   </x:si>
   <x:si>
     <x:t>LCI CEF - NOV/2026</x:t>
@@ -115,19 +115,19 @@
     <x:t>R$ 310.958,77</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 311.228,71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 310.977,67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52,5%|Operações Compromissadas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.210.721,50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52,40%|Pós-Fixada</x:t>
+    <x:t>R$ 311.363,76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 310.999,27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,0%|Operações Compromissadas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 2.761.381,15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57,90%|Pós-Fixada</x:t>
   </x:si>
   <x:si>
     <x:t>17/08/2026</x:t>
@@ -139,22 +139,43 @@
     <x:t>85,00% CDI</x:t>
   </x:si>
   <x:si>
-    <x:t>1.528,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.207.811,80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 2.210.066,82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,1%|Fundos de Investimento</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 467.000,00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,00%|Fundos de Renda Fixa Pós-Fixado</x:t>
+    <x:t>871,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.258.510,52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.260.722,48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.260.224,79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.063.829,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.000,00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.658,67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 1.500.510,47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,81%|Fundos de Investimento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 467.471,34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,80%|Fundos de Renda Fixa Pós-Fixado</x:t>
   </x:si>
   <x:si>
     <x:t>Data cota</x:t>
@@ -172,10 +193,10 @@
     <x:t>Safra DI Master FIRF Referenciado DI LP</x:t>
   </x:si>
   <x:si>
-    <x:t>19/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R$ 271,75</x:t>
+    <x:t>21/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R$ 272,02</x:t>
   </x:si>
   <x:si>
     <x:t>1.718,50</x:t>
@@ -184,10 +205,13 @@
     <x:t>R$ 0,00</x:t>
   </x:si>
   <x:si>
+    <x:t>R$ 467.025,57</x:t>
+  </x:si>
+  <x:si>
     <x:t>0,01%|Saldo projetado</x:t>
   </x:si>
   <x:si>
-    <x:t>R$ 246,52</x:t>
+    <x:t>R$ 517,40</x:t>
   </x:si>
   <x:si>
     <x:t>Resgate de fundo pendente</x:t>
@@ -217,7 +241,7 @@
     <x:t>Saldo Projetado  (D &gt; 3)</x:t>
   </x:si>
   <x:si>
-    <x:t>246,52</x:t>
+    <x:t>517,4</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
@@ -765,10 +789,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K26"/>
+  <x:dimension ref="A1:K27"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="36.996339" style="0" customWidth="1"/>
     <x:col min="2" max="11" width="24.930625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -825,13 +849,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="30" customHeight="1">
       <x:c r="A4" s="6">
-        <x:v>4212287.55969902</x:v>
+        <x:v>4764364.71377368</x:v>
       </x:c>
       <x:c r="B4" s="7">
-        <x:v>4212041.03969902</x:v>
+        <x:v>4763847.31377368</x:v>
       </x:c>
       <x:c r="C4" s="7">
-        <x:v>246.52</x:v>
+        <x:v>517.4</x:v>
       </x:c>
       <x:c r="D4" s="7">
         <x:v>0</x:v>
@@ -1076,242 +1100,271 @@
       <x:c r="K15" s="3"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A16" s="13"/>
-      <x:c r="B16" s="13" t="s">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="13"/>
-      <x:c r="D16" s="13" t="s">
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E16" s="13" t="s">
+      <x:c r="E16" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F16" s="13" t="s">
+      <x:c r="F16" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G16" s="13" t="s">
+      <x:c r="G16" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H16" s="13" t="s">
+      <x:c r="H16" s="12" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="I16" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J16" s="13" t="s">
+      <x:c r="I16" s="12" t="s">
         <x:v>43</x:v>
       </x:c>
+      <x:c r="J16" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="K16" s="3"/>
     </x:row>
-    <x:row r="17" spans="1:11">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9"/>
-      <x:c r="G18" s="10" t="s">
+    <x:row r="17" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A17" s="13"/>
+      <x:c r="B17" s="13" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H18" s="3"/>
-      <x:c r="I18" s="3"/>
-      <x:c r="J18" s="3"/>
-      <x:c r="K18" s="3"/>
-    </x:row>
-    <x:row r="19" spans="1:11">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+      <x:c r="C17" s="13"/>
+      <x:c r="D17" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A19" s="8" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+      <x:c r="E19" s="9"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="G19" s="10" t="s">
+        <x:v>52</x:v>
+      </x:c>
       <x:c r="H19" s="3"/>
       <x:c r="I19" s="3"/>
       <x:c r="J19" s="3"/>
       <x:c r="K19" s="3"/>
     </x:row>
-    <x:row r="20" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A20" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
+    <x:row r="20" spans="1:11">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
       <x:c r="H20" s="3"/>
       <x:c r="I20" s="3"/>
       <x:c r="J20" s="3"/>
       <x:c r="K20" s="3"/>
     </x:row>
-    <x:row r="21" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A21" s="13" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B21" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C21" s="13" t="s">
+    <x:row r="21" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A21" s="11" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D21" s="13" t="s">
+      <x:c r="B21" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
+      <x:c r="C21" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F21" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>45</x:v>
+      <x:c r="D21" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="3"/>
       <x:c r="I21" s="3"/>
       <x:c r="J21" s="3"/>
       <x:c r="K21" s="3"/>
     </x:row>
-    <x:row r="22" spans="1:11">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23" spans="1:11" ht="45" customHeight="1">
-      <x:c r="A23" s="8" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
-      <x:c r="D23" s="9"/>
-      <x:c r="E23" s="9"/>
-      <x:c r="F23" s="9"/>
-      <x:c r="G23" s="9"/>
-      <x:c r="H23" s="9"/>
-      <x:c r="I23" s="9"/>
-      <x:c r="J23" s="9"/>
-      <x:c r="K23" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:11">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25" spans="1:11" ht="35.1" customHeight="1">
-      <x:c r="A25" s="11" t="s">
+    <x:row r="22" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A22" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D22" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G22" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H22" s="3"/>
+      <x:c r="I22" s="3"/>
+      <x:c r="J22" s="3"/>
+      <x:c r="K22" s="3"/>
+    </x:row>
+    <x:row r="23" spans="1:11">
+      <x:c r="A23" s="4"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="4"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="45" customHeight="1">
+      <x:c r="A24" s="8" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B24" s="9"/>
+      <x:c r="C24" s="9"/>
+      <x:c r="D24" s="9"/>
+      <x:c r="E24" s="9"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="G24" s="9"/>
+      <x:c r="H24" s="9"/>
+      <x:c r="I24" s="9"/>
+      <x:c r="J24" s="9"/>
+      <x:c r="K24" s="10" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:11">
+      <x:c r="A25" s="4"/>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="35.1" customHeight="1">
+      <x:c r="A26" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B25" s="11" t="s">
+      <x:c r="B26" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D25" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J25" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K25" s="11" t="s">
+      <x:c r="C26" s="11" t="s">
         <x:v>66</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" spans="1:11" ht="30" customHeight="1">
-      <x:c r="A26" s="13" t="s">
+      <x:c r="D26" s="11" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B26" s="13" t="s">
+      <x:c r="E26" s="11" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="I26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J26" s="13" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K26" s="13" t="s">
-        <x:v>68</x:v>
+      <x:c r="F26" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J26" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K26" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="30" customHeight="1">
+      <x:c r="A27" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="J27" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K27" s="13" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1320,8 +1373,8 @@
     <x:mergeCell ref="F1:G1"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="A13:F13"/>
-    <x:mergeCell ref="A18:F18"/>
-    <x:mergeCell ref="A23:J23"/>
+    <x:mergeCell ref="A19:F19"/>
+    <x:mergeCell ref="A24:J24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
